--- a/src/nodes/LPC/compressor_stage_1_blade_stator_coordinates_lattice.xlsx
+++ b/src/nodes/LPC/compressor_stage_1_blade_stator_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>10.536533041170891</v>
+        <v>10.40620614433465</v>
       </c>
       <c r="B1">
-        <v>11.97486447185049</v>
+        <v>12.088291083874708</v>
       </c>
       <c r="C1">
         <v>384.89451392788493</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>9.66637654797366</v>
+        <v>9.5401152174674255</v>
       </c>
       <c r="B2">
-        <v>11.604239457581004</v>
+        <v>11.708262492511066</v>
       </c>
       <c r="C2">
         <v>384.89451392788493</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>8.8868705905558052</v>
+        <v>8.7656696950549122</v>
       </c>
       <c r="B3">
-        <v>11.141276043535246</v>
+        <v>11.236882822595153</v>
       </c>
       <c r="C3">
         <v>384.89451392788493</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>8.1247044948696168</v>
+        <v>8.0087543353482715</v>
       </c>
       <c r="B4">
-        <v>10.660649908901265</v>
+        <v>10.748029289369812</v>
       </c>
       <c r="C4">
         <v>384.89451392788493</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>7.3757849895761272</v>
+        <v>7.2652309443017993</v>
       </c>
       <c r="B5">
-        <v>10.166530539518732</v>
+        <v>10.245826796768677</v>
       </c>
       <c r="C5">
         <v>384.89451392788493</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>6.638432885990686</v>
+        <v>6.533401904523191</v>
       </c>
       <c r="B6">
-        <v>9.6606283896583172</v>
+        <v>9.7319675101619385</v>
       </c>
       <c r="C6">
         <v>384.89451392788493</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>5.9116834011309818</v>
+        <v>5.8122918447599279</v>
       </c>
       <c r="B7">
-        <v>9.1439262060401774</v>
+        <v>9.20742366832618</v>
       </c>
       <c r="C7">
         <v>384.89451392788493</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>5.1949631320618019</v>
+        <v>5.1013210691121254</v>
       </c>
       <c r="B8">
-        <v>8.61700806805238</v>
+        <v>8.6727731054256161</v>
       </c>
       <c r="C8">
         <v>384.89451392788493</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>4.4873862950873384</v>
+        <v>4.3995940726126781</v>
       </c>
       <c r="B9">
-        <v>8.0807762522045437</v>
+        <v>8.1289084504478186</v>
       </c>
       <c r="C9">
         <v>384.89451392788493</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>3.7879984749185542</v>
+        <v>3.7061459654853723</v>
       </c>
       <c r="B10">
-        <v>7.5362029444827048</v>
+        <v>7.5767914943550858</v>
       </c>
       <c r="C10">
         <v>384.89451392788493</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>3.0958831106540687</v>
+        <v>3.0200501277848089</v>
       </c>
       <c r="B11">
-        <v>6.984221771657003</v>
+        <v>7.0173458811852614</v>
       </c>
       <c r="C11">
         <v>384.89451392788493</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>2.4105460262555871</v>
+        <v>2.3408069600049073</v>
       </c>
       <c r="B12">
-        <v>6.4253361110565583</v>
+        <v>6.4510696059441646</v>
       </c>
       <c r="C12">
         <v>384.89451392788493</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>1.7331447307494985</v>
+        <v>1.6695866745660486</v>
       </c>
       <c r="B13">
-        <v>5.8583669014623236</v>
+        <v>5.8767962144339743</v>
       </c>
       <c r="C13">
         <v>384.89451392788493</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>1.0643682788542435</v>
+        <v>1.0070858884029268</v>
       </c>
       <c r="B14">
-        <v>5.2826122583293076</v>
+        <v>5.293831326956111</v>
       </c>
       <c r="C14">
         <v>384.89451392788493</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>0.40138022299176807</v>
+        <v>0.35043702458099468</v>
       </c>
       <c r="B15">
-        <v>4.7009614423569026</v>
+        <v>4.705033311012583</v>
       </c>
       <c r="C15">
         <v>384.89451392788493</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-0.25842099730778179</v>
+        <v>-0.30299002889438009</v>
       </c>
       <c r="B16">
-        <v>4.11606445366527</v>
+        <v>4.1130238318014767</v>
       </c>
       <c r="C16">
         <v>384.89451392788493</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-0.9131718917850169</v>
+        <v>-0.95131133038897731</v>
       </c>
       <c r="B17">
-        <v>3.526023104813246</v>
+        <v>3.5159249981045697</v>
       </c>
       <c r="C17">
         <v>384.89451392788493</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-1.5604634797730779</v>
+        <v>-1.5920914612299808</v>
       </c>
       <c r="B18">
-        <v>2.928383561215548</v>
+        <v>2.91130921277379</v>
       </c>
       <c r="C18">
         <v>384.89451392788493</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-2.2001698697044909</v>
+        <v>-2.2252031482190651</v>
       </c>
       <c r="B19">
-        <v>2.3230175872717478</v>
+        <v>2.2990496113579826</v>
       </c>
       <c r="C19">
         <v>384.89451392788493</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-2.8327359422866412</v>
+        <v>-2.8510961545265392</v>
       </c>
       <c r="B20">
-        <v>1.7103783471276159</v>
+        <v>1.6795945125802121</v>
       </c>
       <c r="C20">
         <v>384.89451392788493</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-3.4586065782269069</v>
+        <v>-3.4702202433227063</v>
       </c>
       <c r="B21">
-        <v>1.0909190049289328</v>
+        <v>1.0533922351635503</v>
       </c>
       <c r="C21">
         <v>384.89451392788493</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-4.0781471259264492</v>
+        <v>-4.0829447726229775</v>
       </c>
       <c r="B22">
-        <v>0.4650117116666902</v>
+        <v>0.42081095090319665</v>
       </c>
       <c r="C22">
         <v>384.89451392788493</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-4.6914048045615822</v>
+        <v>-4.6893174798232078</v>
       </c>
       <c r="B23">
-        <v>-0.16729543428725158</v>
+        <v>-0.21810175611712385</v>
       </c>
       <c r="C23">
         <v>384.89451392788493</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-5.2983473010023969</v>
+        <v>-5.2893056971643606</v>
       </c>
       <c r="B24">
-        <v>-0.80603534771581675</v>
+        <v>-0.86337844874155489</v>
       </c>
       <c r="C24">
         <v>384.89451392788493</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-5.8989423021189937</v>
+        <v>-5.8828767568874039</v>
       </c>
       <c r="B25">
-        <v>-1.4512409434019329</v>
+        <v>-1.5150516898142443</v>
       </c>
       <c r="C25">
         <v>384.89451392788493</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-6.49314377947619</v>
+        <v>-6.46998412540572</v>
       </c>
       <c r="B26">
-        <v>-2.1029591068053537</v>
+        <v>-2.1731678634757809</v>
       </c>
       <c r="C26">
         <v>384.89451392788493</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-7.0808508434177586</v>
+        <v>-7.0505258058224243</v>
       </c>
       <c r="B27">
-        <v>-2.7612926060932255</v>
+        <v>-2.8378286390526029</v>
       </c>
       <c r="C27">
         <v>384.89451392788493</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-7.661948888982181</v>
+        <v>-7.62438593541304</v>
       </c>
       <c r="B28">
-        <v>-3.4263581801095091</v>
+        <v>-3.5091495071675758</v>
       </c>
       <c r="C28">
         <v>384.89451392788493</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-8.23632331120795</v>
+        <v>-8.1914486514530971</v>
       </c>
       <c r="B29">
-        <v>-4.0982725676981753</v>
+        <v>-4.18724595844358</v>
       </c>
       <c r="C29">
         <v>384.89451392788493</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-8.8039174355293675</v>
+        <v>-8.7516566573866417</v>
       </c>
       <c r="B30">
-        <v>-4.7770934986747129</v>
+        <v>-4.8721751054245006</v>
       </c>
       <c r="C30">
         <v>384.89451392788493</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-9.3649063089639828</v>
+        <v>-9.3051869213317779</v>
       </c>
       <c r="B31">
-        <v>-5.4626426667406838</v>
+        <v>-5.5637605483382551</v>
       </c>
       <c r="C31">
         <v>384.89451392788493</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-9.9195229089251633</v>
+        <v>-9.8522749775751262</v>
       </c>
       <c r="B32">
-        <v>-6.1546827565691746</v>
+        <v>-6.2617675093337724</v>
       </c>
       <c r="C32">
         <v>384.89451392788493</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-10.468000212826263</v>
+        <v>-10.3931563604033</v>
       </c>
       <c r="B33">
-        <v>-6.8529764528332615</v>
+        <v>-6.9659612105599793</v>
       </c>
       <c r="C33">
         <v>384.89451392788493</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-11.010475550684088</v>
+        <v>-10.927969906998293</v>
       </c>
       <c r="B34">
-        <v>-7.5573838685054362</v>
+        <v>-7.6762032607206256</v>
       </c>
       <c r="C34">
         <v>384.89451392788493</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-11.546703662929176</v>
+        <v>-11.45646766612356</v>
       </c>
       <c r="B35">
-        <v>-8.2681548297558223</v>
+        <v>-8.3927408147387688</v>
       </c>
       <c r="C35">
         <v>384.89451392788493</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-12.076343642595505</v>
+        <v>-11.978304989437936</v>
       </c>
       <c r="B36">
-        <v>-8.98563659105395</v>
+        <v>-9.115917414092273</v>
       </c>
       <c r="C36">
         <v>384.89451392788493</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-12.599054582717058</v>
+        <v>-12.493137228600252</v>
       </c>
       <c r="B37">
-        <v>-9.7101764068693566</v>
+        <v>-9.8460766002590248</v>
       </c>
       <c r="C37">
         <v>384.89451392788493</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-13.114262244999738</v>
+        <v>-13.000383843183879</v>
       </c>
       <c r="B38">
-        <v>-10.442359207502912</v>
+        <v>-10.583797049217727</v>
       </c>
       <c r="C38">
         <v>384.89451392788493</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-13.620459065837114</v>
+        <v>-13.498520724420295</v>
       </c>
       <c r="B39">
-        <v>-11.183720626580833</v>
+        <v>-11.330597974950385</v>
       </c>
       <c r="C39">
         <v>384.89451392788493</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-14.1159041502947</v>
+        <v>-13.98578787145553</v>
       </c>
       <c r="B40">
-        <v>-11.936033973560681</v>
+        <v>-12.088233725939837</v>
       </c>
       <c r="C40">
         <v>384.89451392788493</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-14.598856603437989</v>
+        <v>-14.460425283435601</v>
       </c>
       <c r="B41">
-        <v>-12.701072557900009</v>
+        <v>-12.85845865066891</v>
       </c>
       <c r="C41">
         <v>384.89451392788493</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-14.598856603437989</v>
+        <v>-14.460425283435601</v>
       </c>
       <c r="B42">
-        <v>-12.701072557900009</v>
+        <v>-12.85845865066891</v>
       </c>
       <c r="C42">
         <v>384.89451392788493</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-14.034679401678858</v>
+        <v>-13.903671699999602</v>
       </c>
       <c r="B43">
-        <v>-12.018771083109273</v>
+        <v>-12.170086175320314</v>
       </c>
       <c r="C43">
         <v>384.89451392788493</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-13.471959276792076</v>
+        <v>-13.348391184517812</v>
       </c>
       <c r="B44">
-        <v>-11.334985401462088</v>
+        <v>-11.480245362882705</v>
       </c>
       <c r="C44">
         <v>384.89451392788493</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-12.908999364700177</v>
+        <v>-12.792868250221755</v>
       </c>
       <c r="B45">
-        <v>-10.651443971728227</v>
+        <v>-10.790646190713662</v>
       </c>
       <c r="C45">
         <v>384.89451392788493</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-12.344102801325674</v>
+        <v>-12.23538741034295</v>
       </c>
       <c r="B46">
-        <v>-9.9698752526774541</v>
+        <v>-10.102998636170746</v>
       </c>
       <c r="C46">
         <v>384.89451392788493</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-11.775804424718684</v>
+        <v>-11.674467423117791</v>
       </c>
       <c r="B47">
-        <v>-9.2917716867835374</v>
+        <v>-9.41877918390158</v>
       </c>
       <c r="C47">
         <v>384.89451392788493</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-11.203565881439646</v>
+        <v>-11.109564026802174</v>
       </c>
       <c r="B48">
-        <v>-8.6176816513361914</v>
+        <v>-8.73853034771397</v>
       </c>
       <c r="C48">
         <v>384.89451392788493</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-10.627080520176582</v>
+        <v>-10.540367204656855</v>
       </c>
       <c r="B49">
-        <v>-7.947917507329131</v>
+        <v>-8.0625611487057718</v>
       </c>
       <c r="C49">
         <v>384.89451392788493</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-10.04604168961753</v>
+        <v>-9.966566939942604</v>
       </c>
       <c r="B50">
-        <v>-7.2827916157560733</v>
+        <v>-7.3911806079748512</v>
       </c>
       <c r="C50">
         <v>384.89451392788493</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-9.4602366485180891</v>
+        <v>-9.3879481566290472</v>
       </c>
       <c r="B51">
-        <v>-6.62252067898844</v>
+        <v>-6.7246031108192206</v>
       </c>
       <c r="C51">
         <v>384.89451392788493</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-8.869828295904151</v>
+        <v>-8.8046755415212257</v>
       </c>
       <c r="B52">
-        <v>-5.9669387649084884</v>
+        <v>-6.0626644993375223</v>
       </c>
       <c r="C52">
         <v>384.89451392788493</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-8.2750734408691926</v>
+        <v>-8.2170087221330519</v>
       </c>
       <c r="B53">
-        <v>-5.31578428277619</v>
+        <v>-5.4051059798285541</v>
       </c>
       <c r="C53">
         <v>384.89451392788493</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-7.6762288925066731</v>
+        <v>-7.625207325978427</v>
       </c>
       <c r="B54">
-        <v>-4.6687956418515064</v>
+        <v>-4.7516687585911086</v>
       </c>
       <c r="C54">
         <v>384.89451392788493</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-7.0734919174218112</v>
+        <v>-7.0294707846179563</v>
       </c>
       <c r="B55">
-        <v>-4.0257719025316234</v>
+        <v>-4.10215404455359</v>
       </c>
       <c r="C55">
         <v>384.89451392788493</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-6.4668216122667985</v>
+        <v>-6.4297577457990469</v>
       </c>
       <c r="B56">
-        <v>-3.38675472976258</v>
+        <v>-3.4566030571628144</v>
       </c>
       <c r="C56">
         <v>384.89451392788493</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.8561175312055731</v>
+        <v>-5.825966661315805</v>
       </c>
       <c r="B57">
-        <v>-2.7518464396276325</v>
+        <v>-2.815117018495199</v>
       </c>
       <c r="C57">
         <v>384.89451392788493</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-5.2412792284020835</v>
+        <v>-5.2179959829623481</v>
       </c>
       <c r="B58">
-        <v>-2.1211493482100483</v>
+        <v>-2.1777971506271765</v>
       </c>
       <c r="C58">
         <v>384.89451392788493</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.6222184061864979</v>
+        <v>-4.6057564440223278</v>
       </c>
       <c r="B59">
-        <v>-1.4947533972345319</v>
+        <v>-1.5447324335884922</v>
       </c>
       <c r="C59">
         <v>384.89451392788493</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-3.9988953595539809</v>
+        <v>-3.9892079037376584</v>
       </c>
       <c r="B60">
-        <v>-0.87269903099167645</v>
+        <v>-0.91596287922227781</v>
       </c>
       <c r="C60">
         <v>384.89451392788493</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.3712825316659281</v>
+        <v>-3.3683225028398036</v>
       </c>
       <c r="B61">
-        <v>-0.25501431941352581</v>
+        <v>-0.29151625732499215</v>
       </c>
       <c r="C61">
         <v>384.89451392788493</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-2.7393523656837391</v>
+        <v>-2.743072382060229</v>
       </c>
       <c r="B62">
-        <v>0.3582726675678729</v>
+        <v>0.32857966230690294</v>
       </c>
       <c r="C62">
         <v>384.89451392788493</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-2.1031552203446071</v>
+        <v>-2.1135084528116264</v>
       </c>
       <c r="B63">
-        <v>0.96721322634219054</v>
+        <v>0.94437562758038507</v>
       </c>
       <c r="C63">
         <v>384.89451392788493</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-1.4630531166889087</v>
+        <v>-1.4799967092316069</v>
       </c>
       <c r="B64">
-        <v>1.5721761185859722</v>
+        <v>1.5562364572161898</v>
       </c>
       <c r="C64">
         <v>384.89451392788493</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-0.81948599133281852</v>
+        <v>-0.8429819161390103</v>
       </c>
       <c r="B65">
-        <v>2.1736094722974788</v>
+        <v>2.1646054876384886</v>
       </c>
       <c r="C65">
         <v>384.89451392788493</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-0.17289378089250207</v>
+        <v>-0.20290883835266887</v>
       </c>
       <c r="B66">
-        <v>2.7719614154749794</v>
+        <v>2.7699260552714624</v>
       </c>
       <c r="C66">
         <v>384.89451392788493</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>0.47685565617695846</v>
+        <v>0.440356115895244</v>
       </c>
       <c r="B67">
-        <v>3.3670973461693774</v>
+        <v>3.3720649973869836</v>
       </c>
       <c r="C67">
         <v>384.89451392788493</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>1.1321827740648593</v>
+        <v>1.0892599647192385</v>
       </c>
       <c r="B68">
-        <v>3.9565517426421657</v>
+        <v>3.9685831546477393</v>
       </c>
       <c r="C68">
         <v>384.89451392788493</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>1.7949644300622727</v>
+        <v>1.7457001634853016</v>
       </c>
       <c r="B69">
-        <v>4.5384128015336005</v>
+        <v>4.5575891655040861</v>
       </c>
       <c r="C69">
         <v>384.89451392788493</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>2.4626147812229831</v>
+        <v>2.4070624902186268</v>
       </c>
       <c r="B70">
-        <v>5.1153145127883954</v>
+        <v>5.14168885616623</v>
       </c>
       <c r="C70">
         <v>384.89451392788493</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>3.1323145511205315</v>
+        <v>3.0704967275856827</v>
       </c>
       <c r="B71">
-        <v>5.690128646236797</v>
+        <v>5.7237232902868067</v>
       </c>
       <c r="C71">
         <v>384.89451392788493</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>3.8047734296447406</v>
+        <v>3.7367203541587775</v>
       </c>
       <c r="B72">
-        <v>6.26213229794668</v>
+        <v>6.3029772935282775</v>
       </c>
       <c r="C72">
         <v>384.89451392788493</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>4.481171240458357</v>
+        <v>4.40692614189263</v>
       </c>
       <c r="B73">
-        <v>6.8301236765761661</v>
+        <v>6.8782619246100785</v>
       </c>
       <c r="C73">
         <v>384.89451392788493</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5.1610393759995263</v>
+        <v>5.0806403403657194</v>
       </c>
       <c r="B74">
-        <v>7.394580114906721</v>
+        <v>7.45004941246969</v>
       </c>
       <c r="C74">
         <v>384.89451392788493</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5.8434884996003742</v>
+        <v>5.756963852645816</v>
       </c>
       <c r="B75">
-        <v>7.9564075085744577</v>
+        <v>8.0192359665239472</v>
       </c>
       <c r="C75">
         <v>384.89451392788493</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6.5275947893935555</v>
+        <v>6.4349627181341358</v>
       </c>
       <c r="B76">
-        <v>8.51654688051074</v>
+        <v>8.5867525478890361</v>
       </c>
       <c r="C76">
         <v>384.89451392788493</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>7.2125047975702676</v>
+        <v>7.1137741226294589</v>
       </c>
       <c r="B77">
-        <v>9.075867569261451</v>
+        <v>9.1534591997754244</v>
       </c>
       <c r="C77">
         <v>384.89451392788493</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>7.8976810577553493</v>
+        <v>7.7928547011873963</v>
       </c>
       <c r="B78">
-        <v>9.6349170485352538</v>
+        <v>9.7198975420713349</v>
       </c>
       <c r="C78">
         <v>384.89451392788493</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>8.5821963674011918</v>
+        <v>8.4712670754267112</v>
       </c>
       <c r="B79">
-        <v>10.194639784890216</v>
+        <v>10.28700194269895</v>
       </c>
       <c r="C79">
         <v>384.89451392788493</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>9.2644124271109867</v>
+        <v>9.1473549659934275</v>
       </c>
       <c r="B80">
-        <v>10.756704581972729</v>
+        <v>10.856423361750267</v>
       </c>
       <c r="C80">
         <v>384.89451392788493</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>9.9402794490038886</v>
+        <v>9.81702413952086</v>
       </c>
       <c r="B81">
-        <v>11.325236632525844</v>
+        <v>11.432242883662815</v>
       </c>
       <c r="C81">
         <v>384.89451392788493</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>10.536533041170891</v>
+        <v>10.40620614433465</v>
       </c>
       <c r="B82">
-        <v>11.97486447185049</v>
+        <v>12.088291083874708</v>
       </c>
       <c r="C82">
         <v>384.89451392788493</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>10.651432050105969</v>
+        <v>10.482752133122196</v>
       </c>
       <c r="B1">
-        <v>14.083353442799302</v>
+        <v>14.209354546507512</v>
       </c>
       <c r="C1">
         <v>452.5754307907855</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>9.6123579443323539</v>
+        <v>9.3935781802775491</v>
       </c>
       <c r="B2">
-        <v>13.698562844526652</v>
+        <v>13.85915853616557</v>
       </c>
       <c r="C2">
         <v>452.5754307907855</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>8.7483060240826624</v>
+        <v>8.5152881272505052</v>
       </c>
       <c r="B3">
-        <v>13.160036850548611</v>
+        <v>13.328135680974867</v>
       </c>
       <c r="C3">
         <v>452.5754307907855</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>7.9142323912556414</v>
+        <v>7.67202435478311</v>
       </c>
       <c r="B4">
-        <v>12.595178629797722</v>
+        <v>12.767078803244427</v>
       </c>
       <c r="C4">
         <v>452.5754307907855</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>7.1020545815856018</v>
+        <v>6.8539922706703207</v>
       </c>
       <c r="B5">
-        <v>12.011087629915112</v>
+        <v>12.184386482508067</v>
       </c>
       <c r="C5">
         <v>452.5754307907855</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>6.3084659335210995</v>
+        <v>6.0571875470542951</v>
       </c>
       <c r="B6">
-        <v>11.410668345097054</v>
+        <v>11.583492314089558</v>
       </c>
       <c r="C6">
         <v>452.5754307907855</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>5.5315721074096889</v>
+        <v>5.279317871829182</v>
       </c>
       <c r="B7">
-        <v>10.795584719004166</v>
+        <v>10.96636188932076</v>
       </c>
       <c r="C7">
         <v>452.5754307907855</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>4.7702525560248077</v>
+        <v>4.5190289440506772</v>
       </c>
       <c r="B8">
-        <v>10.166821014121609</v>
+        <v>10.334156482091933</v>
       </c>
       <c r="C8">
         <v>452.5754307907855</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>4.0227672068003981</v>
+        <v>3.7742148637294712</v>
       </c>
       <c r="B9">
-        <v>9.525905669508111</v>
+        <v>9.6886818407364625</v>
       </c>
       <c r="C9">
         <v>452.5754307907855</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>3.2872395022290504</v>
+        <v>3.0426040346086753</v>
       </c>
       <c r="B10">
-        <v>8.87448700940384</v>
+        <v>9.0318857933448715</v>
       </c>
       <c r="C10">
         <v>452.5754307907855</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>2.5618664703774154</v>
+        <v>2.3220136744060795</v>
       </c>
       <c r="B11">
-        <v>8.2141487222011449</v>
+        <v>8.365640012593099</v>
       </c>
       <c r="C11">
         <v>452.5754307907855</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>1.8456802769876262</v>
+        <v>1.6112733906677055</v>
       </c>
       <c r="B12">
-        <v>7.5457409308839543</v>
+        <v>7.6909480761599989</v>
       </c>
       <c r="C12">
         <v>452.5754307907855</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>1.1409800529296683</v>
+        <v>0.91317353627781883</v>
       </c>
       <c r="B13">
-        <v>6.8672441326502769</v>
+        <v>7.0054173371507051</v>
       </c>
       <c r="C13">
         <v>452.5754307907855</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>0.44913732747112534</v>
+        <v>0.22937956027271628</v>
       </c>
       <c r="B14">
-        <v>6.1774536082581442</v>
+        <v>6.3076197211851932</v>
       </c>
       <c r="C14">
         <v>452.5754307907855</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-0.23545374165792002</v>
+        <v>-0.44690344904144447</v>
       </c>
       <c r="B15">
-        <v>5.4812933984915642</v>
+        <v>5.6033816685165387</v>
       </c>
       <c r="C15">
         <v>452.5754307907855</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-0.917934787496695</v>
+        <v>-1.1219077333799683</v>
       </c>
       <c r="B16">
-        <v>4.7832797935996423</v>
+        <v>4.8980471461649264</v>
       </c>
       <c r="C16">
         <v>452.5754307907855</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-1.5946132346242066</v>
+        <v>-1.7911544938139046</v>
       </c>
       <c r="B17">
-        <v>4.0801693216658288</v>
+        <v>4.1877757135858911</v>
       </c>
       <c r="C17">
         <v>452.5754307907855</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-2.2607178706653972</v>
+        <v>-2.4488573316069204</v>
       </c>
       <c r="B18">
-        <v>3.3677710612919203</v>
+        <v>3.4676057012189183</v>
       </c>
       <c r="C18">
         <v>452.5754307907855</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-2.91599714388919</v>
+        <v>-3.0947104894374426</v>
       </c>
       <c r="B19">
-        <v>2.645864055318679</v>
+        <v>2.737274931003967</v>
       </c>
       <c r="C19">
         <v>452.5754307907855</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-3.5613294177255117</v>
+        <v>-3.7297783703375949</v>
       </c>
       <c r="B20">
-        <v>1.9152198376466052</v>
+        <v>1.9976960977561029</v>
       </c>
       <c r="C20">
         <v>452.5754307907855</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-4.1975930556042815</v>
+        <v>-4.355125377339494</v>
       </c>
       <c r="B21">
-        <v>1.1766099421762064</v>
+        <v>1.2497818962903995</v>
       </c>
       <c r="C21">
         <v>452.5754307907855</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-4.8255096808463</v>
+        <v>-4.971626064162229</v>
       </c>
       <c r="B22">
-        <v>0.43066822596075222</v>
+        <v>0.49428223112687847</v>
       </c>
       <c r="C22">
         <v>452.5754307907855</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-5.4451739563358661</v>
+        <v>-5.5793955872727521</v>
       </c>
       <c r="B23">
-        <v>-0.32252216133542722</v>
+        <v>-0.268704154394634</v>
       </c>
       <c r="C23">
         <v>452.5754307907855</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-6.0565238048481564</v>
+        <v>-6.17835925382499</v>
       </c>
       <c r="B24">
-        <v>-1.0830157468952397</v>
+        <v>-1.0392413072293634</v>
       </c>
       <c r="C24">
         <v>452.5754307907855</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-6.6594971491583435</v>
+        <v>-6.7684423709728589</v>
       </c>
       <c r="B25">
-        <v>-1.8508670579015871</v>
+        <v>-1.817393274332529</v>
       </c>
       <c r="C25">
         <v>452.5754307907855</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-7.2540053865343976</v>
+        <v>-7.3495382735215768</v>
       </c>
       <c r="B26">
-        <v>-2.6261539209227318</v>
+        <v>-2.6032515180236548</v>
       </c>
       <c r="C26">
         <v>452.5754307907855</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-7.8398538122154662</v>
+        <v>-7.9214124068815481</v>
       </c>
       <c r="B27">
-        <v>-3.4090473600683744</v>
+        <v>-3.3970171620794742</v>
       </c>
       <c r="C27">
         <v>452.5754307907855</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-8.4168211959334851</v>
+        <v>-8.4837982441144657</v>
       </c>
       <c r="B28">
-        <v>-4.1997416988335612</v>
+        <v>-4.198918745641012</v>
       </c>
       <c r="C28">
         <v>452.5754307907855</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-8.9846863074203931</v>
+        <v>-9.0364292582820251</v>
       </c>
       <c r="B29">
-        <v>-4.9984312607133461</v>
+        <v>-5.0091848078492944</v>
       </c>
       <c r="C29">
         <v>452.5754307907855</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-9.5433431758524971</v>
+        <v>-9.57917886735011</v>
       </c>
       <c r="B30">
-        <v>-5.80520912800164</v>
+        <v>-5.8279238891375362</v>
       </c>
       <c r="C30">
         <v>452.5754307907855</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-10.093146868183554</v>
+        <v>-10.112480268901351</v>
       </c>
       <c r="B31">
-        <v>-6.6197634181877945</v>
+        <v>-6.6547645351076863</v>
       </c>
       <c r="C31">
         <v>452.5754307907855</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-10.634567710811712</v>
+        <v>-10.636906605422581</v>
       </c>
       <c r="B32">
-        <v>-7.44168100756004</v>
+        <v>-7.4892152926538964</v>
       </c>
       <c r="C32">
         <v>452.5754307907855</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-11.1680760301351</v>
+        <v>-11.153031019400617</v>
       </c>
       <c r="B33">
-        <v>-8.2705487724065847</v>
+        <v>-8.3307847086703</v>
       </c>
       <c r="C33">
         <v>452.5754307907855</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-11.693953571836403</v>
+        <v>-11.661198212479627</v>
       </c>
       <c r="B34">
-        <v>-9.1061192339070409</v>
+        <v>-9.1791772114665875</v>
       </c>
       <c r="C34">
         <v>452.5754307907855</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-12.211727758736506</v>
+        <v>-12.160839122933144</v>
       </c>
       <c r="B35">
-        <v>-9.9488074928065764</v>
+        <v>-10.034880755014635</v>
       </c>
       <c r="C35">
         <v>452.5754307907855</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-12.720737432940846</v>
+        <v>-12.65115624819204</v>
       </c>
       <c r="B36">
-        <v>-10.799194294741742</v>
+        <v>-10.898579174701862</v>
       </c>
       <c r="C36">
         <v>452.5754307907855</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-13.220321436554867</v>
+        <v>-13.131352085687196</v>
       </c>
       <c r="B37">
-        <v>-11.657860385349112</v>
+        <v>-11.770956305915705</v>
       </c>
       <c r="C37">
         <v>452.5754307907855</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-13.709357549135762</v>
+        <v>-13.600070299486585</v>
       </c>
       <c r="B38">
-        <v>-12.525791496827875</v>
+        <v>-12.653175167489536</v>
       </c>
       <c r="C38">
         <v>452.5754307907855</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-14.184879300047733</v>
+        <v>-14.053719220206563</v>
       </c>
       <c r="B39">
-        <v>-13.405593307627745</v>
+        <v>-13.548315512040528</v>
       </c>
       <c r="C39">
         <v>452.5754307907855</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-14.643459156106749</v>
+        <v>-14.488148345100598</v>
       </c>
       <c r="B40">
-        <v>-14.300276482761072</v>
+        <v>-14.459936275631812</v>
       </c>
       <c r="C40">
         <v>452.5754307907855</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-15.081669584128752</v>
+        <v>-14.899207171422127</v>
       </c>
       <c r="B41">
-        <v>-15.212851687240198</v>
+        <v>-15.3915963943265</v>
       </c>
       <c r="C41">
         <v>452.5754307907855</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-15.081669584128752</v>
+        <v>-14.899207171422127</v>
       </c>
       <c r="B42">
-        <v>-15.212851687240198</v>
+        <v>-15.3915963943265</v>
       </c>
       <c r="C42">
         <v>452.5754307907855</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-14.482737336693722</v>
+        <v>-14.293275923756648</v>
       </c>
       <c r="B43">
-        <v>-14.441450771220493</v>
+        <v>-14.627033740778005</v>
       </c>
       <c r="C43">
         <v>452.5754307907855</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-13.891038362593436</v>
+        <v>-13.697442174682685</v>
       </c>
       <c r="B44">
-        <v>-13.663696317019118</v>
+        <v>-13.853812774230022</v>
       </c>
       <c r="C44">
         <v>452.5754307907855</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-13.303197799282525</v>
+        <v>-13.10760863998437</v>
       </c>
       <c r="B45">
-        <v>-12.882552724990898</v>
+        <v>-13.075446797394859</v>
       </c>
       <c r="C45">
         <v>452.5754307907855</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-12.715840784215587</v>
+        <v>-12.519678035445802</v>
       </c>
       <c r="B46">
-        <v>-12.100984395490636</v>
+        <v>-12.295449112984809</v>
       </c>
       <c r="C46">
         <v>452.5754307907855</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-12.126051567791757</v>
+        <v>-11.93010994033004</v>
       </c>
       <c r="B47">
-        <v>-11.321552454796846</v>
+        <v>-11.516855529384726</v>
       </c>
       <c r="C47">
         <v>452.5754307907855</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-11.532750852188235</v>
+        <v>-11.337591387815957</v>
       </c>
       <c r="B48">
-        <v>-10.54520493288285</v>
+        <v>-10.740791877669738</v>
       </c>
       <c r="C48">
         <v>452.5754307907855</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-10.935318452526735</v>
+        <v>-10.741366274561365</v>
       </c>
       <c r="B49">
-        <v>-9.77248658564565</v>
+        <v>-9.9679064945875044</v>
       </c>
       <c r="C49">
         <v>452.5754307907855</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-10.333134183928973</v>
+        <v>-10.140678497224092</v>
       </c>
       <c r="B50">
-        <v>-9.0039421689822738</v>
+        <v>-9.1988477168857159</v>
       </c>
       <c r="C50">
         <v>452.5754307907855</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-9.7257643637782625</v>
+        <v>-9.5349982932302</v>
       </c>
       <c r="B51">
-        <v>-8.2399526195636312</v>
+        <v>-8.43406980064958</v>
       </c>
       <c r="C51">
         <v>452.5754307907855</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-9.113521318504219</v>
+        <v>-8.9247012630787044</v>
       </c>
       <c r="B52">
-        <v>-7.4802435971561954</v>
+        <v>-7.6732506793144131</v>
       </c>
       <c r="C52">
         <v>452.5754307907855</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-8.4969038767980667</v>
+        <v>-8.310389348036864</v>
       </c>
       <c r="B53">
-        <v>-6.7243769423003474</v>
+        <v>-6.915874205653072</v>
       </c>
       <c r="C53">
         <v>452.5754307907855</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-7.8764108673509989</v>
+        <v>-7.692664489371924</v>
       </c>
       <c r="B54">
-        <v>-5.9719144955364456</v>
+        <v>-6.1614242324383879</v>
       </c>
       <c r="C54">
         <v>452.5754307907855</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-7.2524239312183632</v>
+        <v>-7.0719867351979673</v>
       </c>
       <c r="B55">
-        <v>-5.2225210322843418</v>
+        <v>-5.4095062817181967</v>
       </c>
       <c r="C55">
         <v>452.5754307907855</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-6.6248559589120006</v>
+        <v>-6.4482485610163289</v>
       </c>
       <c r="B56">
-        <v>-4.4762730674817934</v>
+        <v>-4.6602125526402451</v>
       </c>
       <c r="C56">
         <v>452.5754307907855</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.9935026533078846</v>
+        <v>-5.8212005491751677</v>
       </c>
       <c r="B57">
-        <v>-3.733350050946032</v>
+        <v>-3.9137569136272554</v>
       </c>
       <c r="C57">
         <v>452.5754307907855</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-5.3581597172819881</v>
+        <v>-5.1905932820226433</v>
       </c>
       <c r="B58">
-        <v>-2.9939314324942941</v>
+        <v>-3.1703532331019595</v>
       </c>
       <c r="C58">
         <v>452.5754307907855</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.7186475050213241</v>
+        <v>-4.556207420563636</v>
       </c>
       <c r="B59">
-        <v>-2.2581750088085357</v>
+        <v>-2.4301895879088753</v>
       </c>
       <c r="C59">
         <v>452.5754307907855</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.0748849759570973</v>
+        <v>-3.9179439404299448</v>
       </c>
       <c r="B60">
-        <v>-1.5261519640296424</v>
+        <v>-1.6933508885797248</v>
       </c>
       <c r="C60">
         <v>452.5754307907855</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.4268157408315614</v>
+        <v>-3.2757338959101028</v>
       </c>
       <c r="B61">
-        <v>-0.79791182916323211</v>
+        <v>-0.95989625406803314</v>
       </c>
       <c r="C61">
         <v>452.5754307907855</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-2.7743834103869633</v>
+        <v>-2.629508341292635</v>
       </c>
       <c r="B62">
-        <v>-0.073504135214916583</v>
+        <v>-0.22988480332731665</v>
       </c>
       <c r="C62">
         <v>452.5754307907855</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-2.1176864020508548</v>
+        <v>-1.9793862266433622</v>
       </c>
       <c r="B63">
-        <v>0.64715756538264257</v>
+        <v>0.49678545988355738</v>
       </c>
       <c r="C63">
         <v>452.5754307907855</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-1.4574423599919921</v>
+        <v>-1.3262380851372821</v>
       </c>
       <c r="B64">
-        <v>1.3647036344885959</v>
+        <v>1.2208609925843388</v>
       </c>
       <c r="C64">
         <v>452.5754307907855</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-0.79452373506443386</v>
+        <v>-0.67112234572668761</v>
       </c>
       <c r="B65">
-        <v>2.0799004125350429</v>
+        <v>1.9432493669894271</v>
       </c>
       <c r="C65">
         <v>452.5754307907855</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-0.12980297812223168</v>
+        <v>-0.015097437363863599</v>
       </c>
       <c r="B66">
-        <v>2.7935142399540935</v>
+        <v>2.6648581553132318</v>
       </c>
       <c r="C66">
         <v>452.5754307907855</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>0.53697893687692522</v>
+        <v>0.64214994933348779</v>
       </c>
       <c r="B67">
-        <v>3.5053175943262627</v>
+        <v>3.3854187038220496</v>
       </c>
       <c r="C67">
         <v>452.5754307907855</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>1.21060694356083</v>
+        <v>1.3064200770860364</v>
       </c>
       <c r="B68">
-        <v>4.2111075018257376</v>
+        <v>4.0999574549897675</v>
       </c>
       <c r="C68">
         <v>452.5754307907855</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>1.8947896031545479</v>
+        <v>1.9822078969147878</v>
       </c>
       <c r="B69">
-        <v>4.9076264489794408</v>
+        <v>4.80462011832015</v>
       </c>
       <c r="C69">
         <v>452.5754307907855</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>2.5844040796867147</v>
+        <v>2.6633001597036889</v>
       </c>
       <c r="B70">
-        <v>5.5993742151315322</v>
+        <v>5.5047343752288258</v>
       </c>
       <c r="C70">
         <v>452.5754307907855</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>3.2738650665767639</v>
+        <v>3.3429227030651747</v>
       </c>
       <c r="B71">
-        <v>6.2912568029966414</v>
+        <v>6.2061088740388675</v>
       </c>
       <c r="C71">
         <v>452.5754307907855</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>3.9645687720037066</v>
+        <v>4.0227659116626384</v>
       </c>
       <c r="B72">
-        <v>6.9820478159539867</v>
+        <v>6.9072941587912</v>
       </c>
       <c r="C72">
         <v>452.5754307907855</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>4.6588410146206147</v>
+        <v>4.7056471037758394</v>
       </c>
       <c r="B73">
-        <v>7.6697043092768817</v>
+        <v>7.60587446054422</v>
       </c>
       <c r="C73">
         <v>452.5754307907855</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5.355744540217195</v>
+        <v>5.3904267850990086</v>
       </c>
       <c r="B74">
-        <v>8.35504954515043</v>
+        <v>8.3028268627083417</v>
       </c>
       <c r="C74">
         <v>452.5754307907855</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6.0535089376391289</v>
+        <v>6.0749550728336157</v>
       </c>
       <c r="B75">
-        <v>9.0396386113399743</v>
+        <v>8.99999482760378</v>
       </c>
       <c r="C75">
         <v>452.5754307907855</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6.7502942408193327</v>
+        <v>6.7569973427956169</v>
       </c>
       <c r="B76">
-        <v>9.7250876910200024</v>
+        <v>9.6992944808379065</v>
       </c>
       <c r="C76">
         <v>452.5754307907855</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>7.4443990533557916</v>
+        <v>7.4344867734780244</v>
       </c>
       <c r="B77">
-        <v>10.412891251011011</v>
+        <v>10.402498062075756</v>
       </c>
       <c r="C77">
         <v>452.5754307907855</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>8.1347458124194958</v>
+        <v>8.1061124954675989</v>
       </c>
       <c r="B78">
-        <v>11.103995797308338</v>
+        <v>11.110729603925842</v>
       </c>
       <c r="C78">
         <v>452.5754307907855</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>8.81948512977386</v>
+        <v>8.7696276156692363</v>
       </c>
       <c r="B79">
-        <v>11.800025789299871</v>
+        <v>11.825915752231923</v>
       </c>
       <c r="C79">
         <v>452.5754307907855</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>9.4953592548986681</v>
+        <v>9.4210772260400244</v>
       </c>
       <c r="B80">
-        <v>12.503842758875624</v>
+        <v>12.551447726255811</v>
       </c>
       <c r="C80">
         <v>452.5754307907855</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>10.154337739238086</v>
+        <v>10.050719291164064</v>
       </c>
       <c r="B81">
-        <v>13.22250046429331</v>
+        <v>13.295679039604687</v>
       </c>
       <c r="C81">
         <v>452.5754307907855</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>10.651432050105969</v>
+        <v>10.482752133122196</v>
       </c>
       <c r="B82">
-        <v>14.083353442799302</v>
+        <v>14.209354546507512</v>
       </c>
       <c r="C82">
         <v>452.5754307907855</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>10.702879614637537</v>
+        <v>10.507501737564056</v>
       </c>
       <c r="B1">
-        <v>15.867105665829527</v>
+        <v>15.997158544288778</v>
       </c>
       <c r="C1">
         <v>511.37584442281513</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>9.4801037120556781</v>
+        <v>9.165340852180238</v>
       </c>
       <c r="B2">
-        <v>15.483717966397679</v>
+        <v>15.693874695624416</v>
       </c>
       <c r="C2">
         <v>511.37584442281513</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>8.532291501730958</v>
+        <v>8.177962502593898</v>
       </c>
       <c r="B3">
-        <v>14.884421909425981</v>
+        <v>15.118973240740838</v>
       </c>
       <c r="C3">
         <v>511.37584442281513</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>7.6290312875090862</v>
+        <v>7.2463015317399995</v>
       </c>
       <c r="B4">
-        <v>14.250142512564109</v>
+        <v>14.501415173681863</v>
       </c>
       <c r="C4">
         <v>511.37584442281513</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>6.7574957685106085</v>
+        <v>6.35371630295902</v>
       </c>
       <c r="B5">
-        <v>13.590952092785331</v>
+        <v>13.853941148388843</v>
       </c>
       <c r="C5">
         <v>511.37584442281513</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>5.9124439937861322</v>
+        <v>5.4934117579517343</v>
       </c>
       <c r="B6">
-        <v>12.910965975651873</v>
+        <v>13.181753386738926</v>
       </c>
       <c r="C6">
         <v>511.37584442281513</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>5.0908777191784083</v>
+        <v>4.6615032459952443</v>
       </c>
       <c r="B7">
-        <v>12.212538457348005</v>
+        <v>12.487825934588061</v>
       </c>
       <c r="C7">
         <v>511.37584442281513</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>4.2910275010739722</v>
+        <v>3.8557007881732668</v>
       </c>
       <c r="B8">
-        <v>11.497058949185485</v>
+        <v>11.77391197460104</v>
       </c>
       <c r="C8">
         <v>511.37584442281513</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>3.5101386012240106</v>
+        <v>3.0724348195618187</v>
       </c>
       <c r="B9">
-        <v>10.766690540428458</v>
+        <v>11.042744326412629</v>
       </c>
       <c r="C9">
         <v>511.37584442281513</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>2.745238931387417</v>
+        <v>2.307853328287726</v>
       </c>
       <c r="B10">
-        <v>10.023766988982686</v>
+        <v>10.297272047934509</v>
       </c>
       <c r="C10">
         <v>511.37584442281513</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>1.9934722979892474</v>
+        <v>1.5582541006887609</v>
       </c>
       <c r="B11">
-        <v>9.2705310493679338</v>
+        <v>9.5403295132160739</v>
       </c>
       <c r="C11">
         <v>511.37584442281513</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>1.2533087628256376</v>
+        <v>0.821656088473234</v>
       </c>
       <c r="B12">
-        <v>8.5081840672674165</v>
+        <v>8.7734333910346844</v>
       </c>
       <c r="C12">
         <v>511.37584442281513</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>0.528407514510876</v>
+        <v>0.10281310662064265</v>
       </c>
       <c r="B13">
-        <v>7.7338527564041231</v>
+        <v>7.9929442129417634</v>
       </c>
       <c r="C13">
         <v>511.37584442281513</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-0.17904640384053652</v>
+        <v>-0.59543478301918829</v>
       </c>
       <c r="B14">
-        <v>6.945821366359759</v>
+        <v>7.1966876588304034</v>
       </c>
       <c r="C14">
         <v>511.37584442281513</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-0.87795365793140068</v>
+        <v>-1.2846373943863321</v>
       </c>
       <c r="B15">
-        <v>6.1510789221111368</v>
+        <v>6.3935061391863046</v>
       </c>
       <c r="C15">
         <v>511.37584442281513</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.5764778760998031</v>
+        <v>-1.9753881419093646</v>
       </c>
       <c r="B16">
-        <v>5.3560357084910475</v>
+        <v>5.5915098555511324</v>
       </c>
       <c r="C16">
         <v>511.37584442281513</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.2687488284077011</v>
+        <v>-2.660064966181019</v>
       </c>
       <c r="B17">
-        <v>4.5560822743610467</v>
+        <v>4.7848634430977786</v>
       </c>
       <c r="C17">
         <v>511.37584442281513</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-2.9471832610042656</v>
+        <v>-3.3288226628209263</v>
       </c>
       <c r="B18">
-        <v>3.74526405942883</v>
+        <v>3.9660295216659613</v>
       </c>
       <c r="C18">
         <v>511.37584442281513</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.6113796826636739</v>
+        <v>-3.9811389213921835</v>
       </c>
       <c r="B19">
-        <v>2.9232658027578662</v>
+        <v>3.1346082161314621</v>
       </c>
       <c r="C19">
         <v>511.37584442281513</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-4.2627320428163618</v>
+        <v>-4.6188221549437642</v>
       </c>
       <c r="B20">
-        <v>2.0911820682505566</v>
+        <v>2.2919840276290633</v>
       </c>
       <c r="C20">
         <v>511.37584442281513</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-4.9026342908927525</v>
+        <v>-5.2436807765246272</v>
       </c>
       <c r="B21">
-        <v>1.2501074198093221</v>
+        <v>1.4395414572935692</v>
       </c>
       <c r="C21">
         <v>511.37584442281513</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-5.5322318508089214</v>
+        <v>-5.85720091778742</v>
       </c>
       <c r="B22">
-        <v>0.40094127289652148</v>
+        <v>0.57841827116835665</v>
       </c>
       <c r="C22">
         <v>511.37584442281513</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-6.1516760444235015</v>
+        <v>-6.4595795847994726</v>
       </c>
       <c r="B23">
-        <v>-0.456197550785643</v>
+        <v>-0.29123470506880894</v>
       </c>
       <c r="C23">
         <v>511.37584442281513</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-6.7608696680807636</v>
+        <v>-7.0506915022317918</v>
       </c>
       <c r="B24">
-        <v>-1.3213853779750115</v>
+        <v>-1.1695133808315721</v>
       </c>
       <c r="C24">
         <v>511.37584442281513</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-7.3597155181249825</v>
+        <v>-7.6304113947553862</v>
       </c>
       <c r="B25">
-        <v>-2.1946985354094259</v>
+        <v>-2.0565136655335761</v>
       </c>
       <c r="C25">
         <v>511.37584442281513</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-7.9480747176816688</v>
+        <v>-8.1985601900659049</v>
       </c>
       <c r="B26">
-        <v>-3.0762460726787579</v>
+        <v>-2.9523726549609384</v>
       </c>
       <c r="C26">
         <v>511.37584442281513</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-8.5256416970013014</v>
+        <v>-8.7547436279575841</v>
       </c>
       <c r="B27">
-        <v>-3.966267930781012</v>
+        <v>-3.8573921903896955</v>
       </c>
       <c r="C27">
         <v>511.37584442281513</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-9.0920692131155878</v>
+        <v>-9.2985136512493032</v>
       </c>
       <c r="B28">
-        <v>-4.8650367735662208</v>
+        <v>-4.77191529946835</v>
       </c>
       <c r="C28">
         <v>511.37584442281513</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-9.6470100230562448</v>
+        <v>-9.8294222027599361</v>
       </c>
       <c r="B29">
-        <v>-5.7728252648844185</v>
+        <v>-5.6962850098454094</v>
       </c>
       <c r="C29">
         <v>511.37584442281513</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-10.190300472942791</v>
+        <v>-10.347259826583032</v>
       </c>
       <c r="B30">
-        <v>-6.689761909849306</v>
+        <v>-6.630661678658492</v>
       </c>
       <c r="C30">
         <v>511.37584442281513</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-10.722511265245991</v>
+        <v>-10.852771471910813</v>
       </c>
       <c r="B31">
-        <v>-7.6153985786292875</v>
+        <v>-7.57447498100169</v>
       </c>
       <c r="C31">
         <v>511.37584442281513</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-11.244396691524418</v>
+        <v>-11.346940689210172</v>
       </c>
       <c r="B32">
-        <v>-8.54914298265645</v>
+        <v>-8.52697192145822</v>
       </c>
       <c r="C32">
         <v>511.37584442281513</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-11.75671104333664</v>
+        <v>-11.830751028947997</v>
       </c>
       <c r="B33">
-        <v>-9.4904028333628681</v>
+        <v>-9.48739950461129</v>
       </c>
       <c r="C33">
         <v>511.37584442281513</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-12.259909541288391</v>
+        <v>-12.304798174462055</v>
       </c>
       <c r="B34">
-        <v>-10.438820680161175</v>
+        <v>-10.455301681850992</v>
       </c>
       <c r="C34">
         <v>511.37584442281513</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-12.753251122174055</v>
+        <v>-12.768126340573604</v>
       </c>
       <c r="B35">
-        <v>-11.394978424386208</v>
+        <v>-11.431410191794976</v>
       </c>
       <c r="C35">
         <v>511.37584442281513</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-13.235695651835171</v>
+        <v>-13.21939187497477</v>
       </c>
       <c r="B36">
-        <v>-12.359692805353367</v>
+        <v>-12.416753719867771</v>
       </c>
       <c r="C36">
         <v>511.37584442281513</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-13.706202996113293</v>
+        <v>-13.657251125357696</v>
       </c>
       <c r="B37">
-        <v>-13.333780562378058</v>
+        <v>-13.412360951493916</v>
       </c>
       <c r="C37">
         <v>511.37584442281513</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-14.163001038007547</v>
+        <v>-14.079410632989502</v>
       </c>
       <c r="B38">
-        <v>-14.318633205982572</v>
+        <v>-14.419987733447515</v>
       </c>
       <c r="C38">
         <v>511.37584442281513</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-14.601389729147405</v>
+        <v>-14.479777713437279</v>
       </c>
       <c r="B39">
-        <v>-15.317941331516835</v>
+        <v>-15.444298557900918</v>
       </c>
       <c r="C39">
         <v>511.37584442281513</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-15.015937038319903</v>
+        <v>-14.851309875843105</v>
       </c>
       <c r="B40">
-        <v>-16.335970305537657</v>
+        <v>-16.490685078376043</v>
       </c>
       <c r="C40">
         <v>511.37584442281513</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-15.401210934312097</v>
+        <v>-15.186964629349065</v>
       </c>
       <c r="B41">
-        <v>-17.376985494601843</v>
+        <v>-17.564538948394805</v>
       </c>
       <c r="C41">
         <v>511.37584442281513</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-15.401210934312097</v>
+        <v>-15.186964629349065</v>
       </c>
       <c r="B42">
-        <v>-17.376985494601843</v>
+        <v>-17.564538948394805</v>
       </c>
       <c r="C42">
         <v>511.37584442281513</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-14.760604611841847</v>
+        <v>-14.519888973121851</v>
       </c>
       <c r="B43">
-        <v>-16.536463702956784</v>
+        <v>-16.744417275328228</v>
       </c>
       <c r="C43">
         <v>511.37584442281513</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-14.134576201072628</v>
+        <v>-13.87385482690437</v>
       </c>
       <c r="B44">
-        <v>-15.684494971005186</v>
+        <v>-15.908186453689167</v>
       </c>
       <c r="C44">
         <v>511.37584442281513</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-13.517751034949519</v>
+        <v>-13.241877612040586</v>
       </c>
       <c r="B45">
-        <v>-14.825299621534485</v>
+        <v>-15.061193800054914</v>
       </c>
       <c r="C45">
         <v>511.37584442281513</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-12.904754446417615</v>
+        <v>-12.616972749874476</v>
       </c>
       <c r="B46">
-        <v>-13.963097977332136</v>
+        <v>-14.208786631002756</v>
       </c>
       <c r="C46">
         <v>511.37584442281513</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-12.2909416321553</v>
+        <v>-11.993103328820432</v>
       </c>
       <c r="B47">
-        <v>-13.10153725395605</v>
+        <v>-13.355586739626748</v>
       </c>
       <c r="C47">
         <v>511.37584442281513</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-11.674587243774209</v>
+        <v>-11.368023105574553</v>
       </c>
       <c r="B48">
-        <v>-12.241972238046097</v>
+        <v>-12.503313825088014</v>
       </c>
       <c r="C48">
         <v>511.37584442281513</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-11.054695796619273</v>
+        <v>-10.740433503903343</v>
       </c>
       <c r="B49">
-        <v>-11.385184609012615</v>
+        <v>-11.652962063064443</v>
       </c>
       <c r="C49">
         <v>511.37584442281513</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-10.430271806035428</v>
+        <v>-10.109035947573327</v>
       </c>
       <c r="B50">
-        <v>-10.531956046265961</v>
+        <v>-10.805525629233932</v>
       </c>
       <c r="C50">
         <v>511.37584442281513</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-9.8006165959724214</v>
+        <v>-9.4729174435181758</v>
       </c>
       <c r="B51">
-        <v>-9.68283516768809</v>
+        <v>-9.961703501043651</v>
       </c>
       <c r="C51">
         <v>511.37584442281513</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-9.1662187247992328</v>
+        <v>-8.832707331340151</v>
       </c>
       <c r="B52">
-        <v>-8.8374383450474312</v>
+        <v>-9.1210138630178719</v>
       </c>
       <c r="C52">
         <v>511.37584442281513</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-8.5278635594896581</v>
+        <v>-8.1894205338086685</v>
       </c>
       <c r="B53">
-        <v>-7.995148888584021</v>
+        <v>-8.2826797014501388</v>
       </c>
       <c r="C53">
         <v>511.37584442281513</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-7.8863364670174789</v>
+        <v>-7.5440719736931419</v>
       </c>
       <c r="B54">
-        <v>-7.1553501085378892</v>
+        <v>-7.4459240026339906</v>
       </c>
       <c r="C54">
         <v>511.37584442281513</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-7.2422371239199457</v>
+        <v>-6.8974358510637872</v>
       </c>
       <c r="B55">
-        <v>-6.3175711239168937</v>
+        <v>-6.6101540475131335</v>
       </c>
       <c r="C55">
         <v>511.37584442281513</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-6.5954224449881629</v>
+        <v>-6.249323475194049</v>
       </c>
       <c r="B56">
-        <v>-5.4819242888001849</v>
+        <v>-5.7755142956319228</v>
       </c>
       <c r="C56">
         <v>511.37584442281513</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.9455636545766852</v>
+        <v>-5.5993054326581655</v>
       </c>
       <c r="B57">
-        <v>-4.6486677660347322</v>
+        <v>-4.9423335011848666</v>
       </c>
       <c r="C57">
         <v>511.37584442281513</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-5.2923319770400763</v>
+        <v>-4.9469523100303778</v>
       </c>
       <c r="B58">
-        <v>-3.8180597184675054</v>
+        <v>-4.11094041836648</v>
       </c>
       <c r="C58">
         <v>511.37584442281513</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.6354382661103291</v>
+        <v>-4.2918864274925745</v>
       </c>
       <c r="B59">
-        <v>-2.9903271909686819</v>
+        <v>-3.2816241946904108</v>
       </c>
       <c r="C59">
         <v>511.37584442281513</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-3.9747518930291927</v>
+        <v>-3.63393703965723</v>
       </c>
       <c r="B60">
-        <v>-2.1655727565012985</v>
+        <v>-2.45451555094687</v>
       </c>
       <c r="C60">
         <v>511.37584442281513</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.3101818584158522</v>
+        <v>-2.9729851347444658</v>
       </c>
       <c r="B61">
-        <v>-1.3438678700516018</v>
+        <v>-1.6297056012452102</v>
       </c>
       <c r="C61">
         <v>511.37584442281513</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-2.6416371628894937</v>
+        <v>-2.3089117009744049</v>
       </c>
       <c r="B62">
-        <v>-0.52528398660584052</v>
+        <v>-0.80728545969478138</v>
       </c>
       <c r="C62">
         <v>511.37584442281513</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-1.9692732236808652</v>
+        <v>-1.6419178789127313</v>
       </c>
       <c r="B63">
-        <v>0.29030093132663642</v>
+        <v>0.012898864708625245</v>
       </c>
       <c r="C63">
         <v>511.37584442281513</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-1.2942311244669529</v>
+        <v>-0.97348541850736248</v>
       </c>
       <c r="B64">
-        <v>1.1037828911440955</v>
+        <v>0.83198178342347884</v>
       </c>
       <c r="C64">
         <v>511.37584442281513</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-0.61789836553631716</v>
+        <v>-0.30541622205179175</v>
       </c>
       <c r="B65">
-        <v>1.9162513927216844</v>
+        <v>1.6513428130217926</v>
       </c>
       <c r="C65">
         <v>511.37584442281513</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>0.05833755282249535</v>
+        <v>0.36048780816050274</v>
       </c>
       <c r="B66">
-        <v>2.7287959359345719</v>
+        <v>2.4723614700755978</v>
       </c>
       <c r="C66">
         <v>511.37584442281513</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>0.73488627418950669</v>
+        <v>1.0247572128063218</v>
       </c>
       <c r="B67">
-        <v>3.5410948584141204</v>
+        <v>3.2946315784795455</v>
       </c>
       <c r="C67">
         <v>511.37584442281513</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>1.4193460176190487</v>
+        <v>1.6972523044436194</v>
       </c>
       <c r="B68">
-        <v>4.347181848816521</v>
+        <v>4.1106041914188074</v>
       </c>
       <c r="C68">
         <v>511.37584442281513</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>2.1176044475612517</v>
+        <v>2.3856127435570351</v>
       </c>
       <c r="B69">
-        <v>5.1424337659890762</v>
+        <v>4.91443046887509</v>
       </c>
       <c r="C69">
         <v>511.37584442281513</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>2.8215184345751112</v>
+        <v>3.0792658104567781</v>
       </c>
       <c r="B70">
-        <v>5.9332447985186754</v>
+        <v>5.7142047687257067</v>
       </c>
       <c r="C70">
         <v>511.37584442281513</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>3.5222097068084222</v>
+        <v>3.7666842989990226</v>
       </c>
       <c r="B71">
-        <v>6.7265863871714338</v>
+        <v>6.5187521931762813</v>
       </c>
       <c r="C71">
         <v>511.37584442281513</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>4.2218902166552832</v>
+        <v>4.450735437398202</v>
       </c>
       <c r="B72">
-        <v>7.5207216516907422</v>
+        <v>7.3258776238500349</v>
       </c>
       <c r="C72">
         <v>511.37584442281513</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>4.9242482507127594</v>
+        <v>5.1362024166119715</v>
       </c>
       <c r="B73">
-        <v>8.3127544573368741</v>
+        <v>8.1319191023727</v>
       </c>
       <c r="C73">
         <v>511.37584442281513</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5.6277872081434888</v>
+        <v>5.8211378442126032</v>
       </c>
       <c r="B74">
-        <v>9.1038599724603646</v>
+        <v>8.9383675309624468</v>
       </c>
       <c r="C74">
         <v>511.37584442281513</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6.32968638950414</v>
+        <v>6.5018753397721785</v>
       </c>
       <c r="B75">
-        <v>9.89625308070249</v>
+        <v>9.7480298501387175</v>
       </c>
       <c r="C75">
         <v>511.37584442281513</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>7.0270135883619327</v>
+        <v>7.1746031542473911</v>
       </c>
       <c r="B76">
-        <v>10.692236223777178</v>
+        <v>10.563824293033605</v>
       </c>
       <c r="C76">
         <v>511.37584442281513</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>7.717056216715414</v>
+        <v>7.8357942756552976</v>
       </c>
       <c r="B77">
-        <v>11.493939393521783</v>
+        <v>11.388451101218356</v>
       </c>
       <c r="C77">
         <v>511.37584442281513</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>8.398091667277896</v>
+        <v>8.4832060088697929</v>
       </c>
       <c r="B78">
-        <v>12.302715224194667</v>
+        <v>12.223627257408207</v>
       </c>
       <c r="C78">
         <v>511.37584442281513</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>9.0671706711093485</v>
+        <v>9.11300314628306</v>
       </c>
       <c r="B79">
-        <v>13.120879555416549</v>
+        <v>13.072288954354155</v>
       </c>
       <c r="C79">
         <v>511.37584442281513</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>9.7191055561583575</v>
+        <v>9.7184444175080724</v>
       </c>
       <c r="B80">
-        <v>13.952505876828479</v>
+        <v>13.939597234499525</v>
       </c>
       <c r="C80">
         <v>511.37584442281513</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>10.341125673110852</v>
+        <v>10.282945378686604</v>
       </c>
       <c r="B81">
-        <v>14.807622021179883</v>
+        <v>14.838248965606212</v>
       </c>
       <c r="C81">
         <v>511.37584442281513</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>10.702879614637537</v>
+        <v>10.507501737564056</v>
       </c>
       <c r="B82">
-        <v>15.867105665829527</v>
+        <v>15.997158544288778</v>
       </c>
       <c r="C82">
         <v>511.37584442281513</v>
